--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1254,6 +1254,208 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131737820</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93154</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnmyran Öst, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>667427</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7083576</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kollberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131732787</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93116</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnmyran Öst, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>667390</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7083573</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Rask</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93154</v>
+        <v>93155</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93116</v>
+        <v>93117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93155</v>
+        <v>93158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93117</v>
+        <v>93120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93158</v>
+        <v>93164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93120</v>
+        <v>93126</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93164</v>
+        <v>93167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93126</v>
+        <v>93129</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93167</v>
+        <v>93172</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93129</v>
+        <v>93134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93172</v>
+        <v>93174</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93134</v>
+        <v>93136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93174</v>
+        <v>93210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93136</v>
+        <v>93172</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 58293-2025 artfynd.xlsx
+++ b/artfynd/A 58293-2025 artfynd.xlsx
@@ -1259,7 +1259,7 @@
         <v>131737820</v>
       </c>
       <c r="B7" t="n">
-        <v>93215</v>
+        <v>93218</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         <v>131732787</v>
       </c>
       <c r="B8" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
